--- a/data/trans_orig/IP19C07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19C07-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>18190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>25726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35085</t>
+          <t>35154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42661</t>
+          <t>42720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51220</t>
+          <t>50586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56571</t>
+          <t>56568</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58217</t>
+          <t>58481</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64324</t>
+          <t>64320</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112401</t>
+          <t>111838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119613</t>
+          <t>119619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21486</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29759</t>
+          <t>29600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23982</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31521</t>
+          <t>31548</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48037</t>
+          <t>47865</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59499</t>
+          <t>59079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>10764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21009</t>
+          <t>21187</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38622</t>
+          <t>38732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27828</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36996</t>
+          <t>37202</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62591</t>
+          <t>62413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73932</t>
+          <t>74168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21367</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19091</t>
+          <t>19090</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43251</t>
+          <t>42674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48022</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18496</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24016</t>
+          <t>23994</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20663</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40629</t>
+          <t>41285</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49220</t>
+          <t>49814</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50985</t>
+          <t>51178</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59887</t>
+          <t>59955</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>56966</t>
+          <t>57229</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65144</t>
+          <t>65208</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>111148</t>
+          <t>111607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>124227</t>
+          <t>123539</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13784</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>67536</t>
+          <t>66843</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>76288</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65652</t>
+          <t>65623</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72350</t>
+          <t>72373</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136360</t>
+          <t>135416</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>147676</t>
+          <t>147266</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33248</t>
+          <t>34135</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27139</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>46308</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>66442</t>
+          <t>66619</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94353</t>
+          <t>94096</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>297214</t>
+          <t>297809</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>317682</t>
+          <t>316795</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>315738</t>
+          <t>315423</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>334592</t>
+          <t>333558</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>618308</t>
+          <t>618565</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>646219</t>
+          <t>646042</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21041</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28043</t>
+          <t>28343</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49570</t>
+          <t>49668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46999</t>
+          <t>45775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52377</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49145</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55713</t>
+          <t>55767</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98776</t>
+          <t>98533</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106779</t>
+          <t>106832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18425</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>22227</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30028</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28692</t>
+          <t>29206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36733</t>
+          <t>36337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54483</t>
+          <t>54364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64804</t>
+          <t>65373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34911</t>
+          <t>35023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40709</t>
+          <t>40724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34880</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40602</t>
+          <t>40601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72804</t>
+          <t>72836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80500</t>
+          <t>80246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>21608</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21136</t>
+          <t>21159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>26926</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>45540</t>
+          <t>45910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52378</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25678</t>
+          <t>25672</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32843</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25124</t>
+          <t>25593</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>31780</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53471</t>
+          <t>53303</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62991</t>
+          <t>63001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25934</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>49215</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58442</t>
+          <t>58388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52974</t>
+          <t>52749</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62103</t>
+          <t>61983</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>105199</t>
+          <t>104928</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>117962</t>
+          <t>117957</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70386</t>
+          <t>70491</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76622</t>
+          <t>76611</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62656</t>
+          <t>62713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68775</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136101</t>
+          <t>135910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>144616</t>
+          <t>144675</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43994</t>
+          <t>43860</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47275</t>
+          <t>46738</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58006</t>
+          <t>58317</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>85017</t>
+          <t>84678</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>310733</t>
+          <t>310867</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>328970</t>
+          <t>328874</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>318727</t>
+          <t>319264</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>337950</t>
+          <t>338256</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>635712</t>
+          <t>636051</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>662723</t>
+          <t>662412</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>20230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22482</t>
+          <t>22655</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28645</t>
+          <t>28690</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46402</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55068</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43723</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>52039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53223</t>
+          <t>52198</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98369</t>
+          <t>99464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108204</t>
+          <t>108181</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27600</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59974</t>
+          <t>60303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10959</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,8%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>15103</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21152</t>
+          <t>20936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28870</t>
+          <t>28924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,07%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>11332</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30535</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38043</t>
+          <t>37644</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>35113</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69316</t>
+          <t>68981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77457</t>
+          <t>77365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>12128</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>16642</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54551</t>
+          <t>55315</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63557</t>
+          <t>63909</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55518</t>
+          <t>55546</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>61229</t>
+          <t>61244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>113258</t>
+          <t>112744</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>123990</t>
+          <t>123575</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>13821</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>21137</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68400</t>
+          <t>68405</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76117</t>
+          <t>76414</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64429</t>
+          <t>64837</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73892</t>
+          <t>73572</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136722</t>
+          <t>136773</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>148262</t>
+          <t>149037</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>39995</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>40738</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>62906</t>
+          <t>63133</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>323424</t>
+          <t>323401</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>342023</t>
+          <t>341848</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>338732</t>
+          <t>339054</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>353151</t>
+          <t>353520</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>668499</t>
+          <t>668272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>691661</t>
+          <t>690667</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>10192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26947</t>
+          <t>27159</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>33452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34197</t>
+          <t>34165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39287</t>
+          <t>39273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63899</t>
+          <t>64490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71865</t>
+          <t>72144</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>13440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54461</t>
+          <t>55404</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64623</t>
+          <t>64532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60054</t>
+          <t>59778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70950</t>
+          <t>70971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>119479</t>
+          <t>117595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133904</t>
+          <t>133325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>26581</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31198</t>
+          <t>31200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37205</t>
+          <t>37365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65796</t>
+          <t>65580</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71202</t>
+          <t>71195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33351</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>41730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55822</t>
+          <t>55113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90082</t>
+          <t>91060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100174</t>
+          <t>100190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>575</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21036</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31132</t>
+          <t>31086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>54545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59320</t>
+          <t>59344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>24714</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51608</t>
+          <t>50697</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9803</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23886</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>63909</t>
+          <t>64198</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73966</t>
+          <t>74157</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93610</t>
+          <t>94066</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104373</t>
+          <t>104165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>162558</t>
+          <t>162562</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>176641</t>
+          <t>176451</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14331</t>
+          <t>14324</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>75199</t>
+          <t>75193</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82486</t>
+          <t>82516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>87446</t>
+          <t>87453</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>97742</t>
+          <t>97737</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>166897</t>
+          <t>166401</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>178552</t>
+          <t>178778</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41294</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19399</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>38966</t>
+          <t>38241</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>45682</t>
+          <t>45816</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>71610</t>
+          <t>72029</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>350339</t>
+          <t>350576</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>368447</t>
+          <t>369561</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>445478</t>
+          <t>446203</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>465045</t>
+          <t>464469</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>804466</t>
+          <t>804047</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>830394</t>
+          <t>830260</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
